--- a/Software.xlsx
+++ b/Software.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr filterPrivacy="1" showInkAnnotation="0" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{107179A9-9823-4EBA-9AFC-9D969B95604A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4948FF54-9340-42A5-B444-6E6D56C32879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2500" yWindow="3430" windowWidth="22640" windowHeight="16860" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8750" yWindow="650" windowWidth="29080" windowHeight="15460" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Acquisitions" sheetId="18" r:id="rId1"/>
@@ -181,7 +181,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1455" uniqueCount="892">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1455" uniqueCount="893">
   <si>
     <t>Name</t>
   </si>
@@ -2857,6 +2857,9 @@
   </si>
   <si>
     <t>Broadcom</t>
+  </si>
+  <si>
+    <t>Q325</t>
   </si>
 </sst>
 </file>
@@ -5739,17 +5742,17 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="K3">
-            <v>335.59180400000002</v>
+            <v>341</v>
           </cell>
         </row>
         <row r="5">
           <cell r="K5">
-            <v>567.596</v>
+            <v>1667</v>
           </cell>
         </row>
         <row r="6">
           <cell r="K6">
-            <v>3474.4560000000001</v>
+            <v>3512</v>
           </cell>
         </row>
       </sheetData>
@@ -28652,29 +28655,29 @@
         <v>73</v>
       </c>
       <c r="D6" s="204">
-        <v>300.52</v>
+        <v>561</v>
       </c>
       <c r="E6" s="205">
         <f>+D6*H6</f>
-        <v>100852.04893808</v>
+        <v>191301</v>
       </c>
       <c r="F6" s="205">
         <f>+[4]Main!$K$5-[4]Main!$K$6</f>
-        <v>-2906.86</v>
+        <v>-1845</v>
       </c>
       <c r="G6" s="205">
         <f>+E6-F6</f>
-        <v>103758.90893808</v>
+        <v>193146</v>
       </c>
       <c r="H6" s="205">
         <f>+[4]Main!$K$3</f>
-        <v>335.59180400000002</v>
+        <v>341</v>
       </c>
       <c r="I6" s="334" t="s">
-        <v>651</v>
+        <v>892</v>
       </c>
       <c r="J6" s="222">
-        <v>45701</v>
+        <v>46042</v>
       </c>
       <c r="O6" s="212"/>
       <c r="X6" s="203">
